--- a/jupyter/dataloader/templates/Tenant And Branding Master.xlsx
+++ b/jupyter/dataloader/templates/Tenant And Branding Master.xlsx
@@ -3856,6 +3856,7 @@
       <c r="R2" t="n">
         <v>202</v>
       </c>
+      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="12" t="n"/>
@@ -21929,7 +21930,6 @@
       <c r="F2" t="n">
         <v>202</v>
       </c>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="B3" s="16" t="n"/>
